--- a/informe 2/datos1.xlsx
+++ b/informe 2/datos1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srome\OneDrive\Documentos\Universidad\Digital\informes lab\liga-del-autismo-v\informe 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11BADE6-4513-4B7B-A590-B7A606F342A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9F87DD-5706-46C0-B63E-1232BC79044D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,15 +25,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>0.498</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -110,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -129,6 +128,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -422,40 +424,40 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
+      <c r="A2" s="2">
+        <v>0.498</v>
       </c>
       <c r="B2" s="6">
         <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1">
-      <c r="A3" s="3">
-        <v>1251</v>
+      <c r="A3" s="7">
+        <v>1.2509999999999999</v>
       </c>
       <c r="B3" s="6">
         <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1">
-      <c r="A4" s="3">
-        <v>2502</v>
+      <c r="A4" s="7">
+        <v>2.5019999999999998</v>
       </c>
       <c r="B4" s="6">
         <v>512</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1">
-      <c r="A5" s="3">
-        <v>3753</v>
+      <c r="A5" s="7">
+        <v>3.7530000000000001</v>
       </c>
       <c r="B5" s="6">
         <v>768</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1">
-      <c r="A6" s="3">
-        <v>4501</v>
+      <c r="A6" s="7">
+        <v>4.5010000000000003</v>
       </c>
       <c r="B6" s="6">
         <v>921</v>
@@ -463,7 +465,7 @@
     </row>
     <row r="7" spans="1:2" ht="15" thickBot="1">
       <c r="A7" s="3">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="B7" s="6">
         <v>1023</v>

--- a/informe 2/datos1.xlsx
+++ b/informe 2/datos1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srome\OneDrive\Documentos\Universidad\Digital\informes lab\liga-del-autismo-v\informe 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9F87DD-5706-46C0-B63E-1232BC79044D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A14460D-7669-419C-AAD1-958FCCF8F395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,8 +30,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -109,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -129,7 +130,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -412,69 +422,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1">
+    <row r="1" spans="1:3" ht="15" thickBot="1">
       <c r="A1" s="1">
         <v>0</v>
       </c>
       <c r="B1" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15" thickBot="1">
+      <c r="C1" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1">
       <c r="A2" s="2">
         <v>0.498</v>
       </c>
       <c r="B2" s="6">
         <v>102</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" thickBot="1">
+      <c r="C2" s="9">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3" s="7">
         <v>1.2509999999999999</v>
       </c>
       <c r="B3" s="6">
         <v>256</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" thickBot="1">
+      <c r="C3" s="10">
+        <v>1.2509999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1">
       <c r="A4" s="7">
         <v>2.5019999999999998</v>
       </c>
       <c r="B4" s="6">
         <v>512</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" thickBot="1">
+      <c r="C4" s="10">
+        <v>2.5019999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1">
       <c r="A5" s="7">
         <v>3.7530000000000001</v>
       </c>
       <c r="B5" s="6">
         <v>768</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15" thickBot="1">
+      <c r="C5" s="10">
+        <v>3.7530000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6" s="7">
         <v>4.5010000000000003</v>
       </c>
       <c r="B6" s="6">
         <v>921</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15" thickBot="1">
+      <c r="C6" s="10">
+        <v>4.5010000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7" s="6">
         <v>1023</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="15" thickBot="1">
+      <c r="C7" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1">
       <c r="A8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/informe 2/datos1.xlsx
+++ b/informe 2/datos1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srome\OneDrive\Documentos\Universidad\Digital\informes lab\liga-del-autismo-v\informe 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A14460D-7669-419C-AAD1-958FCCF8F395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6670B3A-C225-48AE-8755-1F1F56FAD2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,7 +438,7 @@
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1">
       <c r="A2" s="2">
-        <v>0.498</v>
+        <v>0.499</v>
       </c>
       <c r="B2" s="6">
         <v>102</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="5" spans="1:3" ht="15" thickBot="1">
       <c r="A5" s="7">
-        <v>3.7530000000000001</v>
+        <v>3.754</v>
       </c>
       <c r="B5" s="6">
         <v>768</v>
